--- a/AAII_Financials/Yearly/AGRPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AGRPY_YR_FIN.xlsx
@@ -3296,10 +3296,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>782600</v>
+        <v>846000</v>
       </c>
       <c r="E96" s="3">
-        <v>602000</v>
+        <v>660200</v>
       </c>
       <c r="F96" s="3">
         <v>604900</v>
